--- a/output/pdf_financials_xlsx/PLAN.xlsx
+++ b/output/pdf_financials_xlsx/PLAN.xlsx
@@ -5653,46 +5653,46 @@
         <v>0.800823</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.924223</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.976523</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.088466</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.088466</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.212901</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.624246</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.860386</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.086563</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.141067</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.867149</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>5.564096</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.783852</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>6.218992</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>6.223501</v>
       </c>
     </row>
     <row r="93">
@@ -10166,7 +10166,11 @@
           <t>Share-based payment reserve (Note 18)</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -11560,7 +11564,11 @@
           <t>Share-based payment reserve (Note 19)</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -14810,7 +14818,11 @@
           <t>Share-based payment reserve (Note 10)</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -16218,7 +16230,11 @@
           <t>Share-based payment reserve (Note 9)</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -16778,7 +16794,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -17066,7 +17086,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -17724,7 +17748,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -18296,7 +18324,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>
@@ -18584,7 +18616,11 @@
           <t>Share-based payment reserve (Note 7)</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -19440,7 +19476,11 @@
           <t>Share-based payment reserve (Note 6)</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr"/>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E121" s="5" t="n">
         <v>0.452821</v>
       </c>

--- a/output/pdf_financials_xlsx/PLAN.xlsx
+++ b/output/pdf_financials_xlsx/PLAN.xlsx
@@ -1002,10 +1002,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.005416</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.007041</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1897,10 +1897,10 @@
         <v>-2.727017</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.256954</v>
+        <v>-2.26237</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.562981</v>
+        <v>-1.570022</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-2.957246</v>
@@ -2007,10 +2007,10 @@
         <v>-2.727017</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.256954</v>
+        <v>-2.26237</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.562981</v>
+        <v>-1.570022</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-2.957246</v>
@@ -2279,40 +2279,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.282503</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.153236</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.003385</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.000527</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.002019</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.000317</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.000843</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.271698</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.457414</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.252396</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.101261</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.338583</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>1.770682</v>
@@ -2389,40 +2389,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.307503</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.0575</v>
+        <v>2.210736</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.025</v>
+        <v>0.028385</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.000527</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.021</v>
+        <v>0.023019</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.01125</v>
+        <v>0.011567</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.000843</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.271698</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.457414</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.14415</v>
+        <v>0.396546</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.137988</v>
+        <v>0.239249</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.302</v>
+        <v>1.640583</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>1.770682</v>
@@ -3049,40 +3049,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.312462</v>
+        <v>0.029959</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.16593</v>
+        <v>0.012694</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.012336</v>
+        <v>0.008951000000000001</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.028941</v>
+        <v>0.028414</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.01878</v>
+        <v>0.016761</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.009013</v>
+        <v>0.008696000000000001</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.012519</v>
+        <v>0.011676</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.352459</v>
+        <v>0.080761</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.518001</v>
+        <v>0.060587</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.295472</v>
+        <v>0.043076</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.143592</v>
+        <v>0.042331</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.372602</v>
+        <v>0.034019</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.599561</v>
@@ -7418,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009183</v>
       </c>
       <c r="L124" s="3" t="n">
         <v>0</v>
@@ -7427,16 +7427,16 @@
         <v>0</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.823708</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-1.480333</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.003546</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.000225</v>
       </c>
     </row>
     <row r="125">
@@ -7473,7 +7473,7 @@
         <v>0</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009183</v>
       </c>
       <c r="L125" s="3" t="n">
         <v>0</v>
@@ -7482,16 +7482,16 @@
         <v>0</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.823708</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-1.480333</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.003546</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.000225</v>
       </c>
     </row>
     <row r="126">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
@@ -22482,7 +22482,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -29588,7 +29592,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr"/>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E230" t="inlineStr">
         <is>
           <t>-</t>
@@ -30982,7 +30990,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D245" t="inlineStr"/>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -47068,7 +47080,7 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -50744,7 +50756,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -53508,7 +53520,7 @@
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
@@ -65570,7 +65582,7 @@
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E609" t="inlineStr">
@@ -66046,7 +66058,7 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
@@ -66334,7 +66346,7 @@
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
@@ -66628,7 +66640,7 @@
       </c>
       <c r="D620" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E620" s="5" t="n">
@@ -66918,7 +66930,7 @@
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">

--- a/output/pdf_financials_xlsx/PLAN.xlsx
+++ b/output/pdf_financials_xlsx/PLAN.xlsx
@@ -751,13 +751,13 @@
         <v>0.445972</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.229103</v>
+        <v>0.285103</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.157977</v>
+        <v>0.204977</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.336557</v>
+        <v>0.396557</v>
       </c>
       <c r="N7" s="3" t="n">
         <v>0.932548</v>
@@ -916,7 +916,7 @@
         <v>0.448997</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.314102</v>
+        <v>0.370102</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>1.812947</v>
@@ -971,7 +971,7 @@
         <v>-0.448997</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.314102</v>
+        <v>-0.370102</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>-1.812947</v>
@@ -2645,16 +2645,16 @@
         <v>0</v>
       </c>
       <c r="N40" s="3" t="n">
-        <v>0</v>
+        <v>0.148895</v>
       </c>
       <c r="O40" s="3" t="n">
-        <v>0</v>
+        <v>0.047411</v>
       </c>
       <c r="P40" s="3" t="n">
-        <v>0</v>
+        <v>0.042513</v>
       </c>
       <c r="Q40" s="3" t="n">
-        <v>0</v>
+        <v>0.048998</v>
       </c>
     </row>
     <row r="41">
@@ -2700,16 +2700,16 @@
         <v>0.068777</v>
       </c>
       <c r="N41" s="3" t="n">
-        <v>2.200046</v>
+        <v>2.348941</v>
       </c>
       <c r="O41" s="3" t="n">
-        <v>1.675691</v>
+        <v>1.723102</v>
       </c>
       <c r="P41" s="3" t="n">
-        <v>1.341426</v>
+        <v>1.383939</v>
       </c>
       <c r="Q41" s="3" t="n">
-        <v>1.355931</v>
+        <v>1.404929</v>
       </c>
     </row>
     <row r="42">
@@ -3085,16 +3085,16 @@
         <v>0.034019</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.599561</v>
+        <v>0.450666</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.201546</v>
+        <v>0.154135</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.224313</v>
+        <v>0.1818</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.602074</v>
+        <v>0.553076</v>
       </c>
     </row>
     <row r="49">
@@ -4190,40 +4190,40 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.0525</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.025</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.0255</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.0255</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.0255</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.030058</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.043898</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.041432</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.036</v>
       </c>
       <c r="N67" s="3" t="n">
         <v>0</v>
@@ -4397,10 +4397,10 @@
         <v>0</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>2.404265</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>1.590631</v>
       </c>
     </row>
     <row r="71">
@@ -4452,10 +4452,10 @@
         <v>6.365937</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>6.140571</v>
+        <v>8.544836</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>5.839779</v>
+        <v>7.43041</v>
       </c>
     </row>
     <row r="72">
@@ -4965,10 +4965,10 @@
         <v>0.4992560102085767</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.4724861649063449</v>
+        <v>0.657482307654072</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.4060501114003092</v>
+        <v>0.5166494842099283</v>
       </c>
     </row>
     <row r="81">
@@ -6437,16 +6437,16 @@
         <v>0.05682</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>0.022909</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>1.090417</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>0.373581</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>1.806227</v>
       </c>
     </row>
     <row r="107">
@@ -6630,16 +6630,16 @@
         <v>0</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.003415</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.003745</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>0.004132</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.003396</v>
       </c>
       <c r="I110" s="3" t="n">
         <v>0</v>
@@ -6697,7 +6697,7 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012049</v>
       </c>
       <c r="J111" s="3" t="n">
         <v>0</v>
@@ -6773,10 +6773,10 @@
         <v>0</v>
       </c>
       <c r="P112" s="3" t="n">
-        <v>0</v>
+        <v>0.249252</v>
       </c>
       <c r="Q112" s="3" t="n">
-        <v>0</v>
+        <v>1.346941</v>
       </c>
     </row>
     <row r="113">
@@ -6899,22 +6899,22 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.017218</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.026235</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.0021</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.008</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.0107</v>
       </c>
       <c r="I115" s="3" t="n">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.082327</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.118</v>
       </c>
       <c r="N115" s="3" t="n">
         <v>0</v>
@@ -7994,7 +7994,7 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012049</v>
       </c>
       <c r="J134" s="3" t="n">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>-0.002298</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-1.008092</v>
+        <v>-1.020141</v>
       </c>
       <c r="J135" s="3" t="n">
         <v>-0.690712</v>
@@ -9688,7 +9688,11 @@
           <t>Lease obligations (Note 14)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -21476,7 +21480,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -21568,7 +21576,11 @@
           <t>Net change in non-cash operating working capital (Note 23)</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
           <t>-</t>
@@ -21854,7 +21866,11 @@
           <t>Proceeds from disposition of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -23946,7 +23962,11 @@
           <t>Net change in non-cash operating working capital (Note 24)</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -24974,7 +24994,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -27058,7 +27082,11 @@
           <t>Proceeds from the sales of marketable securities</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -27344,7 +27372,11 @@
           <t>Proceeds from share issuances, net</t>
         </is>
       </c>
-      <c r="D206" t="inlineStr"/>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -28442,7 +28474,11 @@
           <t>Fair value allocated to warrants in private placement $</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr"/>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
@@ -30350,7 +30386,11 @@
           <t>Fair value allocated to warrants in private placement $</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -30636,7 +30676,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -31844,7 +31888,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -32514,7 +32562,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -33078,7 +33130,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -33174,7 +33230,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -33536,7 +33596,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D272" t="inlineStr"/>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E272" t="inlineStr">
         <is>
           <t>-</t>
@@ -34016,7 +34080,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -36104,7 +36172,11 @@
           <t>Proceeds on share issuance</t>
         </is>
       </c>
-      <c r="D299" t="inlineStr"/>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E299" s="5" t="n">
         <v>1.8354</v>
       </c>
@@ -37846,7 +37918,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D317" t="inlineStr"/>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E317" s="5" t="n">
         <v>-0.075</v>
       </c>
@@ -44898,7 +44974,11 @@
           <t>Deferred income tax recovery (Note 18)</t>
         </is>
       </c>
-      <c r="D391" t="inlineStr"/>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E391" t="inlineStr">
         <is>
           <t>-</t>
@@ -47176,7 +47256,11 @@
           <t>Management and director fees (Note 12)</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr"/>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E415" t="inlineStr">
         <is>
           <t>-</t>
@@ -50948,7 +51032,11 @@
           <t>Management and director fees (Note 11)</t>
         </is>
       </c>
-      <c r="D455" t="inlineStr"/>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E455" t="inlineStr">
         <is>
           <t>-</t>
@@ -67600,7 +67688,11 @@
           <t>Future income tax recovery (Note 11)</t>
         </is>
       </c>
-      <c r="D630" t="inlineStr"/>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E630" s="5" t="n">
         <v>0.075</v>
       </c>
